--- a/knowledge/wifi.xlsx
+++ b/knowledge/wifi.xlsx
@@ -397,11 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Network Name</v>
+        <v>Network Name (SSID)</v>
       </c>
       <c r="B1" t="str">
         <v>Password</v>
@@ -410,21 +410,30 @@
         <v>Login Required</v>
       </c>
       <c r="D1" t="str">
-        <v>Username</v>
+        <v>Login Username</v>
       </c>
       <c r="E1" t="str">
         <v>Login Password</v>
       </c>
       <c r="F1" t="str">
-        <v>Notes</v>
+        <v>Location / Notes</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Access Level</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Allowed Users</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Network Name</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Aechs_Unifi</v>
+        <v>AECHS_UNIFI</v>
       </c>
       <c r="B2" t="str">
-        <v>Aechs@1025</v>
+        <v>Aechs@1925</v>
       </c>
       <c r="C2" t="str">
         <v>Yes</v>
@@ -436,32 +445,151 @@
         <v>223344@55</v>
       </c>
       <c r="F2" t="str">
-        <v>If login page does not appear, open browser and visit any http:// website</v>
+        <v>Main school network — all buildings. After connecting, open browser for login portal.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>all_staff</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Bookstore</v>
+        <v>AECHS-office</v>
       </c>
       <c r="B3" t="str">
-        <v>123456</v>
+        <v>4813#3746@</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>4813#3746@</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>Main office network — DSL router source. Router login password same as WiFi password.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>office</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AECHS_Office2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>11@22$bs</v>
+      </c>
+      <c r="C4" t="str">
+        <v>No</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Office area — network 2</v>
+      </c>
+      <c r="G4" t="str">
+        <v>office</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BookStore</v>
+      </c>
+      <c r="B5" t="str">
+        <v>11@22$bs</v>
+      </c>
+      <c r="C5" t="str">
+        <v>No</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Bookstore area</v>
+      </c>
+      <c r="G5" t="str">
+        <v>named</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Mrs. Tamar Ohanian</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Church_WiFi</v>
+      </c>
+      <c r="B6" t="str">
+        <v>&lt;&lt;FILL — check church router&gt;&gt;</v>
+      </c>
+      <c r="C6" t="str">
+        <v>No</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Church / Chapel</v>
+      </c>
+      <c r="G6" t="str">
+        <v>named</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Mr. Yeghia Boghossian | Pastor</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Robotics_Room_WiFi</v>
+      </c>
+      <c r="B7" t="str">
+        <v>&lt;&lt;FILL — check robotics room router&gt;&gt;</v>
+      </c>
+      <c r="C7" t="str">
+        <v>No</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Robotics classroom</v>
+      </c>
+      <c r="G7" t="str">
+        <v>named</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Mr. Yeghia Boghossian | Mr. Jawad Mestrah | Miss Alik Stanboulian</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>